--- a/AER_2024/whole_list_manually_labled.xlsx
+++ b/AER_2024/whole_list_manually_labled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhushangkai/Desktop/seasonal_liquidity/AER_2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B011F3-8CFD-2848-B054-BF09988C5390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0B76D2-0628-0E40-AC45-B0550454F064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="760" windowWidth="25380" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3432,6 +3432,9 @@
   <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="54.33203125" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" customWidth="1"/>
+    <col min="3" max="3" width="50.83203125" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="21.33203125" customWidth="1"/>
     <col min="11" max="11" width="8.83203125" customWidth="1"/>
@@ -3544,6 +3547,15 @@
       <c r="J3" s="2" t="s">
         <v>884</v>
       </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -3576,6 +3588,15 @@
       <c r="J4" s="2" t="s">
         <v>885</v>
       </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -3608,6 +3629,15 @@
       <c r="J5" s="2" t="s">
         <v>886</v>
       </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -3639,6 +3669,15 @@
       </c>
       <c r="J6" s="2" t="s">
         <v>887</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">

--- a/AER_2024/whole_list_manually_labled.xlsx
+++ b/AER_2024/whole_list_manually_labled.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhushangkai/Desktop/seasonal_liquidity/AER_2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2658F6A4-1BD9-B44F-9B18-875207A95CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4351622F-1454-A54C-BBE6-6E70E2D40300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3847,7 +3860,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4158,7 +4171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q124"/>
+  <dimension ref="A1:Q125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -10401,6 +10414,24 @@
       </c>
       <c r="Q124">
         <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="M125">
+        <f t="shared" ref="M125:O125" si="0">SUM(M3:M124)</f>
+        <v>11</v>
+      </c>
+      <c r="N125">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="O125">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="P125">
+        <f>SUM(P3:P124)</f>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -10749,5 +10780,6 @@
     <hyperlink ref="J124" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>